--- a/ULA/ULA_Producto.xlsx
+++ b/ULA/ULA_Producto.xlsx
@@ -2801,13 +2801,13 @@
         <v>0.0380403501546397</v>
       </c>
       <c r="L2" s="2">
-        <v>112.2262160580291</v>
+        <v>111.0917574884164</v>
       </c>
       <c r="M2" s="2">
-        <v>0.6098749364825251</v>
+        <v>0.6037099077362396</v>
       </c>
       <c r="N2" s="2">
-        <v>0.04269124555377676</v>
+        <v>0.04225969354153677</v>
       </c>
     </row>
     <row r="3" spans="1:14">
